--- a/output/yearly_population_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_7_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5799</v>
+        <v>6732</v>
       </c>
       <c r="C2" t="n">
-        <v>8960</v>
+        <v>12311</v>
       </c>
       <c r="D2" t="n">
-        <v>24403</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4066</v>
+        <v>3857</v>
       </c>
       <c r="C3" t="n">
-        <v>5803</v>
+        <v>4065</v>
       </c>
       <c r="D3" t="n">
-        <v>17616</v>
+        <v>14089</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2981</v>
+        <v>2938</v>
       </c>
       <c r="C4" t="n">
-        <v>3713</v>
+        <v>3943</v>
       </c>
       <c r="D4" t="n">
-        <v>8445</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1913</v>
+        <v>2050</v>
       </c>
       <c r="C5" t="n">
-        <v>3006</v>
+        <v>3553</v>
       </c>
       <c r="D5" t="n">
-        <v>2879</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1090</v>
+        <v>1231</v>
       </c>
       <c r="C6" t="n">
-        <v>2301</v>
+        <v>3490</v>
       </c>
       <c r="D6" t="n">
-        <v>1157</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>490</v>
+        <v>603</v>
       </c>
       <c r="C7" t="n">
-        <v>1361</v>
+        <v>2649</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="C8" t="n">
-        <v>617</v>
+        <v>1447</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>559</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6589</v>
+        <v>8328</v>
       </c>
       <c r="C2" t="n">
-        <v>9364</v>
+        <v>9333</v>
       </c>
       <c r="D2" t="n">
-        <v>23080</v>
+        <v>27967</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3969</v>
+        <v>4125</v>
       </c>
       <c r="C3" t="n">
-        <v>6401</v>
+        <v>6855</v>
       </c>
       <c r="D3" t="n">
-        <v>17381</v>
+        <v>13974</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2962</v>
+        <v>2841</v>
       </c>
       <c r="C4" t="n">
-        <v>4679</v>
+        <v>3879</v>
       </c>
       <c r="D4" t="n">
-        <v>9773</v>
+        <v>7232</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2127</v>
+        <v>2150</v>
       </c>
       <c r="C5" t="n">
-        <v>3253</v>
+        <v>3620</v>
       </c>
       <c r="D5" t="n">
-        <v>3699</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1321</v>
+        <v>1436</v>
       </c>
       <c r="C6" t="n">
-        <v>2609</v>
+        <v>3484</v>
       </c>
       <c r="D6" t="n">
-        <v>1394</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>673</v>
+        <v>783</v>
       </c>
       <c r="C7" t="n">
-        <v>1793</v>
+        <v>2984</v>
       </c>
       <c r="D7" t="n">
-        <v>727</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="C8" t="n">
-        <v>938</v>
+        <v>1952</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C9" t="n">
-        <v>434</v>
+        <v>910</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9143</v>
+        <v>9242</v>
       </c>
       <c r="C2" t="n">
-        <v>9231</v>
+        <v>9824</v>
       </c>
       <c r="D2" t="n">
-        <v>20530</v>
+        <v>31914</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4171</v>
+        <v>4679</v>
       </c>
       <c r="C3" t="n">
-        <v>6777</v>
+        <v>6970</v>
       </c>
       <c r="D3" t="n">
-        <v>16970</v>
+        <v>14758</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2883</v>
+        <v>2849</v>
       </c>
       <c r="C4" t="n">
-        <v>5313</v>
+        <v>5018</v>
       </c>
       <c r="D4" t="n">
-        <v>10550</v>
+        <v>7913</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2197</v>
+        <v>2182</v>
       </c>
       <c r="C5" t="n">
-        <v>3783</v>
+        <v>3616</v>
       </c>
       <c r="D5" t="n">
-        <v>4519</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1508</v>
+        <v>1564</v>
       </c>
       <c r="C6" t="n">
-        <v>2862</v>
+        <v>3508</v>
       </c>
       <c r="D6" t="n">
-        <v>1693</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>849</v>
+        <v>929</v>
       </c>
       <c r="C7" t="n">
-        <v>2118</v>
+        <v>3149</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>382</v>
+        <v>441</v>
       </c>
       <c r="C8" t="n">
-        <v>1289</v>
+        <v>2326</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C9" t="n">
-        <v>627</v>
+        <v>1297</v>
       </c>
       <c r="D9" t="n">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>314</v>
+        <v>551</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8178</v>
+        <v>8479</v>
       </c>
       <c r="C2" t="n">
-        <v>6129</v>
+        <v>6758</v>
       </c>
       <c r="D2" t="n">
-        <v>16911</v>
+        <v>26239</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5157</v>
+        <v>5337</v>
       </c>
       <c r="C3" t="n">
-        <v>9852</v>
+        <v>9911</v>
       </c>
       <c r="D3" t="n">
-        <v>18943</v>
+        <v>15890</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2030</v>
+        <v>2016</v>
       </c>
       <c r="C4" t="n">
-        <v>6640</v>
+        <v>6169</v>
       </c>
       <c r="D4" t="n">
-        <v>10068</v>
+        <v>7455</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1393</v>
+        <v>1445</v>
       </c>
       <c r="C5" t="n">
-        <v>2804</v>
+        <v>3437</v>
       </c>
       <c r="D5" t="n">
-        <v>2917</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>858</v>
       </c>
       <c r="C6" t="n">
-        <v>2075</v>
+        <v>3086</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>1263</v>
+        <v>2279</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>614</v>
+        <v>1271</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>539</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>158</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4856</v>
+        <v>5196</v>
       </c>
       <c r="C2" t="n">
-        <v>3540</v>
+        <v>4059</v>
       </c>
       <c r="D2" t="n">
-        <v>12796</v>
+        <v>18085</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5603</v>
+        <v>5692</v>
       </c>
       <c r="C3" t="n">
-        <v>7327</v>
+        <v>7745</v>
       </c>
       <c r="D3" t="n">
-        <v>17710</v>
+        <v>16534</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2817</v>
+        <v>2805</v>
       </c>
       <c r="C4" t="n">
-        <v>8298</v>
+        <v>7906</v>
       </c>
       <c r="D4" t="n">
-        <v>11318</v>
+        <v>8514</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>1573</v>
       </c>
       <c r="C5" t="n">
-        <v>4500</v>
+        <v>4632</v>
       </c>
       <c r="D5" t="n">
-        <v>3776</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>950</v>
+        <v>1011</v>
       </c>
       <c r="C6" t="n">
-        <v>2439</v>
+        <v>3392</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="C7" t="n">
-        <v>1604</v>
+        <v>2662</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>812</v>
+        <v>1620</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>578</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4463</v>
+        <v>5035</v>
       </c>
       <c r="C2" t="n">
-        <v>5361</v>
+        <v>6553</v>
       </c>
       <c r="D2" t="n">
-        <v>15333</v>
+        <v>23468</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4430</v>
+        <v>4607</v>
       </c>
       <c r="C3" t="n">
-        <v>4806</v>
+        <v>5373</v>
       </c>
       <c r="D3" t="n">
-        <v>15783</v>
+        <v>15633</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3492</v>
+        <v>3470</v>
       </c>
       <c r="C4" t="n">
-        <v>7711</v>
+        <v>7664</v>
       </c>
       <c r="D4" t="n">
-        <v>12078</v>
+        <v>9564</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="C5" t="n">
-        <v>6229</v>
+        <v>6044</v>
       </c>
       <c r="D5" t="n">
-        <v>4892</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1106</v>
+        <v>1143</v>
       </c>
       <c r="C6" t="n">
-        <v>3364</v>
+        <v>3940</v>
       </c>
       <c r="D6" t="n">
-        <v>1426</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="C7" t="n">
-        <v>1995</v>
+        <v>2968</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>2053</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>546</v>
+        <v>977</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2643</v>
+        <v>3039</v>
       </c>
       <c r="C2" t="n">
-        <v>2450</v>
+        <v>3131</v>
       </c>
       <c r="D2" t="n">
-        <v>10618</v>
+        <v>16355</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4279</v>
+        <v>4542</v>
       </c>
       <c r="C3" t="n">
-        <v>4839</v>
+        <v>5605</v>
       </c>
       <c r="D3" t="n">
-        <v>15353</v>
+        <v>16097</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3867</v>
+        <v>3826</v>
       </c>
       <c r="C4" t="n">
-        <v>7360</v>
+        <v>7514</v>
       </c>
       <c r="D4" t="n">
-        <v>12646</v>
+        <v>10291</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C5" t="n">
-        <v>7395</v>
+        <v>7288</v>
       </c>
       <c r="D5" t="n">
-        <v>5299</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>933</v>
+        <v>963</v>
       </c>
       <c r="C6" t="n">
-        <v>4189</v>
+        <v>4879</v>
       </c>
       <c r="D6" t="n">
-        <v>1396</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>2106</v>
+        <v>3337</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>907</v>
+        <v>1581</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3482</v>
+        <v>4875</v>
       </c>
       <c r="C2" t="n">
-        <v>9579</v>
+        <v>6469</v>
       </c>
       <c r="D2" t="n">
-        <v>9590</v>
+        <v>15930</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3075</v>
+        <v>3357</v>
       </c>
       <c r="C3" t="n">
-        <v>3295</v>
+        <v>3996</v>
       </c>
       <c r="D3" t="n">
-        <v>13677</v>
+        <v>15204</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3533</v>
+        <v>3628</v>
       </c>
       <c r="C4" t="n">
-        <v>6043</v>
+        <v>6531</v>
       </c>
       <c r="D4" t="n">
-        <v>12703</v>
+        <v>10869</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2427</v>
+        <v>2386</v>
       </c>
       <c r="C5" t="n">
-        <v>7296</v>
+        <v>7306</v>
       </c>
       <c r="D5" t="n">
-        <v>6266</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="C6" t="n">
-        <v>5575</v>
+        <v>5877</v>
       </c>
       <c r="D6" t="n">
-        <v>1953</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>3003</v>
+        <v>3972</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1370</v>
+        <v>2263</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>487</v>
+        <v>744</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2472</v>
+        <v>3199</v>
       </c>
       <c r="C2" t="n">
-        <v>5489</v>
+        <v>4224</v>
       </c>
       <c r="D2" t="n">
-        <v>8264</v>
+        <v>11558</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2810</v>
+        <v>3367</v>
       </c>
       <c r="C3" t="n">
-        <v>5296</v>
+        <v>4502</v>
       </c>
       <c r="D3" t="n">
-        <v>12442</v>
+        <v>14464</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3099</v>
+        <v>3269</v>
       </c>
       <c r="C4" t="n">
-        <v>4930</v>
+        <v>5561</v>
       </c>
       <c r="D4" t="n">
-        <v>12569</v>
+        <v>11329</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2651</v>
+        <v>2620</v>
       </c>
       <c r="C5" t="n">
-        <v>6955</v>
+        <v>7159</v>
       </c>
       <c r="D5" t="n">
-        <v>6937</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1407</v>
       </c>
       <c r="C6" t="n">
-        <v>6354</v>
+        <v>6551</v>
       </c>
       <c r="D6" t="n">
-        <v>2340</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>3863</v>
+        <v>4652</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1776</v>
+        <v>2788</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>833</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4318</v>
+        <v>4366</v>
       </c>
       <c r="C2" t="n">
-        <v>7839</v>
+        <v>7619</v>
       </c>
       <c r="D2" t="n">
-        <v>12798</v>
+        <v>15968</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2259</v>
+        <v>2782</v>
       </c>
       <c r="C3" t="n">
-        <v>4816</v>
+        <v>3907</v>
       </c>
       <c r="D3" t="n">
-        <v>11210</v>
+        <v>13189</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2602</v>
+        <v>2898</v>
       </c>
       <c r="C4" t="n">
-        <v>4938</v>
+        <v>4998</v>
       </c>
       <c r="D4" t="n">
-        <v>12047</v>
+        <v>11436</v>
       </c>
     </row>
     <row r="5">
@@ -3624,10 +3624,10 @@
         <v>2589</v>
       </c>
       <c r="C5" t="n">
-        <v>5954</v>
+        <v>6365</v>
       </c>
       <c r="D5" t="n">
-        <v>7537</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1725</v>
+        <v>1686</v>
       </c>
       <c r="C6" t="n">
-        <v>6602</v>
+        <v>6729</v>
       </c>
       <c r="D6" t="n">
-        <v>2927</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="C7" t="n">
-        <v>4813</v>
+        <v>5357</v>
       </c>
       <c r="D7" t="n">
-        <v>975</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>2549</v>
+        <v>3471</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>982</v>
+        <v>1473</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>417</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4875</v>
+        <v>8844</v>
       </c>
       <c r="C2" t="n">
-        <v>3316</v>
+        <v>17819</v>
       </c>
       <c r="D2" t="n">
-        <v>10456</v>
+        <v>7435</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3056</v>
+        <v>3159</v>
       </c>
       <c r="C2" t="n">
-        <v>4390</v>
+        <v>4388</v>
       </c>
       <c r="D2" t="n">
-        <v>9419</v>
+        <v>11753</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3159</v>
+        <v>3657</v>
       </c>
       <c r="C3" t="n">
-        <v>5949</v>
+        <v>5082</v>
       </c>
       <c r="D3" t="n">
-        <v>12390</v>
+        <v>14451</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3693</v>
+        <v>3875</v>
       </c>
       <c r="C4" t="n">
-        <v>7067</v>
+        <v>7189</v>
       </c>
       <c r="D4" t="n">
-        <v>12492</v>
+        <v>11622</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1689</v>
+        <v>1605</v>
       </c>
       <c r="C5" t="n">
-        <v>9055</v>
+        <v>9369</v>
       </c>
       <c r="D5" t="n">
-        <v>6933</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="C6" t="n">
-        <v>6075</v>
+        <v>6568</v>
       </c>
       <c r="D6" t="n">
-        <v>2265</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>2498</v>
+        <v>3401</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>962</v>
+        <v>1443</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6324</v>
+        <v>8331</v>
       </c>
       <c r="C2" t="n">
-        <v>4992</v>
+        <v>6809</v>
       </c>
       <c r="D2" t="n">
-        <v>13145</v>
+        <v>11460</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2072</v>
+        <v>3755</v>
       </c>
       <c r="C3" t="n">
-        <v>1697</v>
+        <v>8980</v>
       </c>
       <c r="D3" t="n">
-        <v>2395</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6037</v>
+        <v>5717</v>
       </c>
       <c r="C2" t="n">
-        <v>5582</v>
+        <v>5055</v>
       </c>
       <c r="D2" t="n">
-        <v>19713</v>
+        <v>12739</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3445</v>
+        <v>4966</v>
       </c>
       <c r="C3" t="n">
-        <v>3095</v>
+        <v>6684</v>
       </c>
       <c r="D3" t="n">
-        <v>4024</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>933</v>
+        <v>1665</v>
       </c>
       <c r="C4" t="n">
-        <v>1053</v>
+        <v>5304</v>
       </c>
       <c r="D4" t="n">
-        <v>1664</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,10 +4980,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5485</v>
+        <v>6054</v>
       </c>
       <c r="C2" t="n">
-        <v>5010</v>
+        <v>5836</v>
       </c>
       <c r="D2" t="n">
-        <v>24247</v>
+        <v>15931</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3911</v>
+        <v>4395</v>
       </c>
       <c r="C3" t="n">
-        <v>3852</v>
+        <v>5040</v>
       </c>
       <c r="D3" t="n">
-        <v>6244</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1851</v>
+        <v>2782</v>
       </c>
       <c r="C4" t="n">
-        <v>2177</v>
+        <v>5962</v>
       </c>
       <c r="D4" t="n">
-        <v>2066</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>443</v>
+        <v>731</v>
       </c>
       <c r="C5" t="n">
-        <v>679</v>
+        <v>2950</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5896</v>
+        <v>6195</v>
       </c>
       <c r="C2" t="n">
-        <v>4916</v>
+        <v>4887</v>
       </c>
       <c r="D2" t="n">
-        <v>34766</v>
+        <v>28008</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3828</v>
+        <v>4287</v>
       </c>
       <c r="C3" t="n">
-        <v>3874</v>
+        <v>4745</v>
       </c>
       <c r="D3" t="n">
-        <v>8540</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2417</v>
+        <v>3012</v>
       </c>
       <c r="C4" t="n">
-        <v>3048</v>
+        <v>5351</v>
       </c>
       <c r="D4" t="n">
-        <v>2745</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>954</v>
+        <v>1427</v>
       </c>
       <c r="C5" t="n">
-        <v>1455</v>
+        <v>4421</v>
       </c>
       <c r="D5" t="n">
-        <v>1341</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>257</v>
+        <v>370</v>
       </c>
       <c r="C6" t="n">
-        <v>488</v>
+        <v>1594</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6374</v>
+        <v>6591</v>
       </c>
       <c r="C2" t="n">
-        <v>4514</v>
+        <v>4123</v>
       </c>
       <c r="D2" t="n">
-        <v>41834</v>
+        <v>35288</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3532</v>
+        <v>3774</v>
       </c>
       <c r="C3" t="n">
-        <v>3615</v>
+        <v>3950</v>
       </c>
       <c r="D3" t="n">
-        <v>11218</v>
+        <v>8232</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1951</v>
+        <v>2255</v>
       </c>
       <c r="C4" t="n">
-        <v>2879</v>
+        <v>4068</v>
       </c>
       <c r="D4" t="n">
-        <v>3222</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>872</v>
+        <v>1143</v>
       </c>
       <c r="C5" t="n">
-        <v>1671</v>
+        <v>3562</v>
       </c>
       <c r="D5" t="n">
-        <v>1261</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>288</v>
+        <v>415</v>
       </c>
       <c r="C6" t="n">
-        <v>663</v>
+        <v>1994</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>269</v>
+        <v>595</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6114</v>
+        <v>5580</v>
       </c>
       <c r="C2" t="n">
-        <v>5778</v>
+        <v>6630</v>
       </c>
       <c r="D2" t="n">
-        <v>32452</v>
+        <v>25563</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4167</v>
+        <v>4264</v>
       </c>
       <c r="C3" t="n">
-        <v>3560</v>
+        <v>3485</v>
       </c>
       <c r="D3" t="n">
-        <v>15762</v>
+        <v>12171</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2392</v>
+        <v>2600</v>
       </c>
       <c r="C4" t="n">
-        <v>3271</v>
+        <v>3913</v>
       </c>
       <c r="D4" t="n">
-        <v>4812</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1267</v>
+        <v>1509</v>
       </c>
       <c r="C5" t="n">
-        <v>2355</v>
+        <v>3779</v>
       </c>
       <c r="D5" t="n">
-        <v>1618</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>538</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>1235</v>
+        <v>2843</v>
       </c>
       <c r="D6" t="n">
-        <v>838</v>
+        <v>814</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>490</v>
+        <v>1362</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>248</v>
+        <v>420</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5652</v>
+        <v>5495</v>
       </c>
       <c r="C2" t="n">
-        <v>9051</v>
+        <v>4841</v>
       </c>
       <c r="D2" t="n">
-        <v>27410</v>
+        <v>24870</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4220</v>
+        <v>4031</v>
       </c>
       <c r="C3" t="n">
-        <v>4140</v>
+        <v>4461</v>
       </c>
       <c r="D3" t="n">
-        <v>17297</v>
+        <v>13349</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>2940</v>
       </c>
       <c r="C4" t="n">
-        <v>3369</v>
+        <v>3559</v>
       </c>
       <c r="D4" t="n">
-        <v>6721</v>
+        <v>4993</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1598</v>
+        <v>1785</v>
       </c>
       <c r="C5" t="n">
-        <v>2793</v>
+        <v>3772</v>
       </c>
       <c r="D5" t="n">
-        <v>2182</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>1833</v>
+        <v>3296</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>891</v>
+        <v>2116</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>877</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_7_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6732</v>
+        <v>7197</v>
       </c>
       <c r="C2" t="n">
-        <v>12311</v>
+        <v>4633</v>
       </c>
       <c r="D2" t="n">
-        <v>20417</v>
+        <v>34156</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3857</v>
+        <v>4152</v>
       </c>
       <c r="C3" t="n">
-        <v>4065</v>
+        <v>5226</v>
       </c>
       <c r="D3" t="n">
-        <v>14089</v>
+        <v>15446</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2938</v>
+        <v>3179</v>
       </c>
       <c r="C4" t="n">
-        <v>3943</v>
+        <v>4718</v>
       </c>
       <c r="D4" t="n">
-        <v>6285</v>
+        <v>8060</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2050</v>
+        <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>3553</v>
+        <v>3355</v>
       </c>
       <c r="D5" t="n">
-        <v>2190</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1231</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>3490</v>
+        <v>2404</v>
       </c>
       <c r="D6" t="n">
-        <v>1014</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>603</v>
+        <v>501</v>
       </c>
       <c r="C7" t="n">
-        <v>2649</v>
+        <v>1394</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>1447</v>
+        <v>618</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>559</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8328</v>
+        <v>8473</v>
       </c>
       <c r="C2" t="n">
-        <v>9333</v>
+        <v>10406</v>
       </c>
       <c r="D2" t="n">
-        <v>27967</v>
+        <v>25696</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4125</v>
+        <v>4527</v>
       </c>
       <c r="C3" t="n">
-        <v>6855</v>
+        <v>4348</v>
       </c>
       <c r="D3" t="n">
-        <v>13974</v>
+        <v>16952</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2841</v>
+        <v>3083</v>
       </c>
       <c r="C4" t="n">
-        <v>3879</v>
+        <v>4868</v>
       </c>
       <c r="D4" t="n">
-        <v>7232</v>
+        <v>8942</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2150</v>
+        <v>2218</v>
       </c>
       <c r="C5" t="n">
-        <v>3620</v>
+        <v>3894</v>
       </c>
       <c r="D5" t="n">
-        <v>2752</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1358</v>
       </c>
       <c r="C6" t="n">
-        <v>3484</v>
+        <v>2818</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>783</v>
+        <v>671</v>
       </c>
       <c r="C7" t="n">
-        <v>2984</v>
+        <v>1835</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="C8" t="n">
-        <v>1952</v>
+        <v>959</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>910</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9242</v>
+        <v>9108</v>
       </c>
       <c r="C2" t="n">
-        <v>9824</v>
+        <v>6523</v>
       </c>
       <c r="D2" t="n">
-        <v>31914</v>
+        <v>33164</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4679</v>
+        <v>4996</v>
       </c>
       <c r="C3" t="n">
-        <v>6970</v>
+        <v>6124</v>
       </c>
       <c r="D3" t="n">
-        <v>14758</v>
+        <v>16959</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2849</v>
+        <v>3132</v>
       </c>
       <c r="C4" t="n">
-        <v>5018</v>
+        <v>4532</v>
       </c>
       <c r="D4" t="n">
-        <v>7913</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2182</v>
+        <v>2289</v>
       </c>
       <c r="C5" t="n">
-        <v>3616</v>
+        <v>4196</v>
       </c>
       <c r="D5" t="n">
-        <v>3313</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1564</v>
+        <v>1573</v>
       </c>
       <c r="C6" t="n">
-        <v>3508</v>
+        <v>3218</v>
       </c>
       <c r="D6" t="n">
-        <v>1347</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>929</v>
+        <v>848</v>
       </c>
       <c r="C7" t="n">
-        <v>3149</v>
+        <v>2248</v>
       </c>
       <c r="D7" t="n">
-        <v>737</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>441</v>
+        <v>384</v>
       </c>
       <c r="C8" t="n">
-        <v>2326</v>
+        <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="C9" t="n">
-        <v>1297</v>
+        <v>635</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>551</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8479</v>
+        <v>8318</v>
       </c>
       <c r="C2" t="n">
-        <v>6758</v>
+        <v>4383</v>
       </c>
       <c r="D2" t="n">
-        <v>26239</v>
+        <v>26917</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5337</v>
+        <v>5903</v>
       </c>
       <c r="C3" t="n">
-        <v>9911</v>
+        <v>8497</v>
       </c>
       <c r="D3" t="n">
-        <v>15890</v>
+        <v>18840</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2016</v>
+        <v>2115</v>
       </c>
       <c r="C4" t="n">
-        <v>6169</v>
+        <v>6595</v>
       </c>
       <c r="D4" t="n">
-        <v>7455</v>
+        <v>9541</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="C5" t="n">
-        <v>3437</v>
+        <v>3153</v>
       </c>
       <c r="D5" t="n">
-        <v>2210</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>3086</v>
+        <v>2203</v>
       </c>
       <c r="D6" t="n">
-        <v>722</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>354</v>
       </c>
       <c r="C7" t="n">
-        <v>2279</v>
+        <v>1274</v>
       </c>
       <c r="D7" t="n">
-        <v>455</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>1271</v>
+        <v>622</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>539</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>158</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>4962</v>
       </c>
       <c r="C2" t="n">
-        <v>4059</v>
+        <v>2181</v>
       </c>
       <c r="D2" t="n">
-        <v>18085</v>
+        <v>19520</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5692</v>
+        <v>5997</v>
       </c>
       <c r="C3" t="n">
-        <v>7745</v>
+        <v>5936</v>
       </c>
       <c r="D3" t="n">
-        <v>16534</v>
+        <v>18853</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2805</v>
+        <v>3093</v>
       </c>
       <c r="C4" t="n">
-        <v>7906</v>
+        <v>7624</v>
       </c>
       <c r="D4" t="n">
-        <v>8514</v>
+        <v>10862</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1573</v>
+        <v>1623</v>
       </c>
       <c r="C5" t="n">
-        <v>4632</v>
+        <v>4692</v>
       </c>
       <c r="D5" t="n">
-        <v>2861</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1011</v>
+        <v>944</v>
       </c>
       <c r="C6" t="n">
-        <v>3392</v>
+        <v>2652</v>
       </c>
       <c r="D6" t="n">
-        <v>863</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>2662</v>
+        <v>1649</v>
       </c>
       <c r="D7" t="n">
-        <v>493</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>1620</v>
+        <v>830</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5035</v>
+        <v>4942</v>
       </c>
       <c r="C2" t="n">
-        <v>6553</v>
+        <v>3242</v>
       </c>
       <c r="D2" t="n">
-        <v>23468</v>
+        <v>20266</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4607</v>
+        <v>4659</v>
       </c>
       <c r="C3" t="n">
-        <v>5373</v>
+        <v>3660</v>
       </c>
       <c r="D3" t="n">
-        <v>15633</v>
+        <v>17651</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3470</v>
+        <v>3778</v>
       </c>
       <c r="C4" t="n">
-        <v>7664</v>
+        <v>6622</v>
       </c>
       <c r="D4" t="n">
-        <v>9564</v>
+        <v>11912</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1852</v>
+        <v>1998</v>
       </c>
       <c r="C5" t="n">
-        <v>6044</v>
+        <v>6001</v>
       </c>
       <c r="D5" t="n">
-        <v>3642</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="C6" t="n">
-        <v>3940</v>
+        <v>3591</v>
       </c>
       <c r="D6" t="n">
-        <v>1139</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>551</v>
+        <v>505</v>
       </c>
       <c r="C7" t="n">
-        <v>2968</v>
+        <v>2106</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>2053</v>
+        <v>1174</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>977</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3039</v>
+        <v>2923</v>
       </c>
       <c r="C2" t="n">
-        <v>3131</v>
+        <v>1508</v>
       </c>
       <c r="D2" t="n">
-        <v>16355</v>
+        <v>13979</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4542</v>
+        <v>4560</v>
       </c>
       <c r="C3" t="n">
-        <v>5605</v>
+        <v>3389</v>
       </c>
       <c r="D3" t="n">
-        <v>16097</v>
+        <v>17520</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3826</v>
+        <v>4165</v>
       </c>
       <c r="C4" t="n">
-        <v>7514</v>
+        <v>6159</v>
       </c>
       <c r="D4" t="n">
-        <v>10291</v>
+        <v>12672</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1953</v>
+        <v>2074</v>
       </c>
       <c r="C5" t="n">
-        <v>7288</v>
+        <v>6960</v>
       </c>
       <c r="D5" t="n">
-        <v>3859</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>963</v>
+        <v>940</v>
       </c>
       <c r="C6" t="n">
-        <v>4879</v>
+        <v>4421</v>
       </c>
       <c r="D6" t="n">
-        <v>1125</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>3337</v>
+        <v>2194</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1581</v>
+        <v>906</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4875</v>
+        <v>4397</v>
       </c>
       <c r="C2" t="n">
-        <v>6469</v>
+        <v>2568</v>
       </c>
       <c r="D2" t="n">
-        <v>15930</v>
+        <v>11430</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3357</v>
+        <v>3313</v>
       </c>
       <c r="C3" t="n">
-        <v>3996</v>
+        <v>2221</v>
       </c>
       <c r="D3" t="n">
-        <v>15204</v>
+        <v>15861</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3628</v>
+        <v>3789</v>
       </c>
       <c r="C4" t="n">
-        <v>6531</v>
+        <v>4733</v>
       </c>
       <c r="D4" t="n">
-        <v>10869</v>
+        <v>13077</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2386</v>
+        <v>2596</v>
       </c>
       <c r="C5" t="n">
-        <v>7306</v>
+        <v>6512</v>
       </c>
       <c r="D5" t="n">
-        <v>4667</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1208</v>
+        <v>1257</v>
       </c>
       <c r="C6" t="n">
-        <v>5877</v>
+        <v>5519</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C7" t="n">
-        <v>3972</v>
+        <v>3152</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2263</v>
+        <v>1403</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>744</v>
+        <v>485</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3199</v>
+        <v>3062</v>
       </c>
       <c r="C2" t="n">
-        <v>4224</v>
+        <v>2149</v>
       </c>
       <c r="D2" t="n">
-        <v>11558</v>
+        <v>8351</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3367</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>4502</v>
+        <v>2139</v>
       </c>
       <c r="D3" t="n">
-        <v>14464</v>
+        <v>14466</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3269</v>
+        <v>3356</v>
       </c>
       <c r="C4" t="n">
-        <v>5561</v>
+        <v>3709</v>
       </c>
       <c r="D4" t="n">
-        <v>11329</v>
+        <v>13179</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2620</v>
+        <v>2837</v>
       </c>
       <c r="C5" t="n">
-        <v>7159</v>
+        <v>5960</v>
       </c>
       <c r="D5" t="n">
-        <v>5224</v>
+        <v>6931</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1407</v>
+        <v>1497</v>
       </c>
       <c r="C6" t="n">
-        <v>6551</v>
+        <v>6065</v>
       </c>
       <c r="D6" t="n">
-        <v>1778</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C7" t="n">
-        <v>4652</v>
+        <v>3970</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2788</v>
+        <v>1831</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>833</v>
+        <v>587</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4366</v>
+        <v>4743</v>
       </c>
       <c r="C2" t="n">
-        <v>7619</v>
+        <v>4073</v>
       </c>
       <c r="D2" t="n">
-        <v>15968</v>
+        <v>18865</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2782</v>
+        <v>2659</v>
       </c>
       <c r="C3" t="n">
-        <v>3907</v>
+        <v>1899</v>
       </c>
       <c r="D3" t="n">
-        <v>13189</v>
+        <v>12734</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2898</v>
+        <v>2873</v>
       </c>
       <c r="C4" t="n">
-        <v>4998</v>
+        <v>2938</v>
       </c>
       <c r="D4" t="n">
-        <v>11436</v>
+        <v>12976</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2589</v>
+        <v>2757</v>
       </c>
       <c r="C5" t="n">
-        <v>6365</v>
+        <v>4885</v>
       </c>
       <c r="D5" t="n">
-        <v>5885</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1686</v>
+        <v>1833</v>
       </c>
       <c r="C6" t="n">
-        <v>6729</v>
+        <v>5969</v>
       </c>
       <c r="D6" t="n">
-        <v>2185</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>649</v>
       </c>
       <c r="C7" t="n">
-        <v>5357</v>
+        <v>4828</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>986</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>3471</v>
+        <v>2605</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1473</v>
+        <v>1019</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>417</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8844</v>
+        <v>5831</v>
       </c>
       <c r="C2" t="n">
-        <v>17819</v>
+        <v>3580</v>
       </c>
       <c r="D2" t="n">
-        <v>7435</v>
+        <v>12808</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3159</v>
+        <v>3359</v>
       </c>
       <c r="C2" t="n">
-        <v>4388</v>
+        <v>2248</v>
       </c>
       <c r="D2" t="n">
-        <v>11753</v>
+        <v>13884</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3657</v>
+        <v>3602</v>
       </c>
       <c r="C3" t="n">
-        <v>5082</v>
+        <v>2596</v>
       </c>
       <c r="D3" t="n">
-        <v>14451</v>
+        <v>14179</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3875</v>
+        <v>4012</v>
       </c>
       <c r="C4" t="n">
-        <v>7189</v>
+        <v>4511</v>
       </c>
       <c r="D4" t="n">
-        <v>11622</v>
+        <v>13465</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1605</v>
+        <v>1795</v>
       </c>
       <c r="C5" t="n">
-        <v>9369</v>
+        <v>7798</v>
       </c>
       <c r="D5" t="n">
-        <v>5307</v>
+        <v>6995</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>547</v>
+        <v>599</v>
       </c>
       <c r="C6" t="n">
-        <v>6568</v>
+        <v>6018</v>
       </c>
       <c r="D6" t="n">
-        <v>1756</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>3401</v>
+        <v>2552</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1443</v>
+        <v>998</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8331</v>
+        <v>6245</v>
       </c>
       <c r="C2" t="n">
-        <v>6809</v>
+        <v>5168</v>
       </c>
       <c r="D2" t="n">
-        <v>11460</v>
+        <v>18227</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3755</v>
+        <v>2477</v>
       </c>
       <c r="C3" t="n">
-        <v>8980</v>
+        <v>1804</v>
       </c>
       <c r="D3" t="n">
-        <v>1888</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5717</v>
+        <v>4682</v>
       </c>
       <c r="C2" t="n">
-        <v>5055</v>
+        <v>4642</v>
       </c>
       <c r="D2" t="n">
-        <v>12739</v>
+        <v>25528</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4966</v>
+        <v>3582</v>
       </c>
       <c r="C3" t="n">
-        <v>6684</v>
+        <v>3238</v>
       </c>
       <c r="D3" t="n">
-        <v>3357</v>
+        <v>5178</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1665</v>
+        <v>1109</v>
       </c>
       <c r="C4" t="n">
-        <v>5304</v>
+        <v>1101</v>
       </c>
       <c r="D4" t="n">
-        <v>1561</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
         <v>172</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6054</v>
+        <v>6390</v>
       </c>
       <c r="C2" t="n">
-        <v>5836</v>
+        <v>7159</v>
       </c>
       <c r="D2" t="n">
-        <v>15931</v>
+        <v>22305</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4395</v>
+        <v>3391</v>
       </c>
       <c r="C3" t="n">
-        <v>5040</v>
+        <v>3465</v>
       </c>
       <c r="D3" t="n">
-        <v>4616</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2782</v>
+        <v>1986</v>
       </c>
       <c r="C4" t="n">
-        <v>5962</v>
+        <v>2288</v>
       </c>
       <c r="D4" t="n">
-        <v>1858</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>731</v>
+        <v>515</v>
       </c>
       <c r="C5" t="n">
-        <v>2950</v>
+        <v>695</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6195</v>
+        <v>6058</v>
       </c>
       <c r="C2" t="n">
-        <v>4887</v>
+        <v>4312</v>
       </c>
       <c r="D2" t="n">
-        <v>28008</v>
+        <v>27897</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4287</v>
+        <v>3933</v>
       </c>
       <c r="C3" t="n">
-        <v>4745</v>
+        <v>4694</v>
       </c>
       <c r="D3" t="n">
-        <v>6010</v>
+        <v>9658</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3012</v>
+        <v>2271</v>
       </c>
       <c r="C4" t="n">
-        <v>5351</v>
+        <v>2884</v>
       </c>
       <c r="D4" t="n">
-        <v>2304</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1427</v>
+        <v>1044</v>
       </c>
       <c r="C5" t="n">
-        <v>4421</v>
+        <v>1521</v>
       </c>
       <c r="D5" t="n">
-        <v>1298</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>1594</v>
+        <v>499</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6591</v>
+        <v>7246</v>
       </c>
       <c r="C2" t="n">
-        <v>4123</v>
+        <v>5810</v>
       </c>
       <c r="D2" t="n">
-        <v>35288</v>
+        <v>34661</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3774</v>
+        <v>3629</v>
       </c>
       <c r="C3" t="n">
-        <v>3950</v>
+        <v>3679</v>
       </c>
       <c r="D3" t="n">
-        <v>8232</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2255</v>
+        <v>1937</v>
       </c>
       <c r="C4" t="n">
-        <v>4068</v>
+        <v>3198</v>
       </c>
       <c r="D4" t="n">
-        <v>2484</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1143</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>3562</v>
+        <v>1639</v>
       </c>
       <c r="D5" t="n">
-        <v>1160</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>415</v>
+        <v>318</v>
       </c>
       <c r="C6" t="n">
-        <v>1994</v>
+        <v>679</v>
       </c>
       <c r="D6" t="n">
-        <v>745</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>595</v>
+        <v>272</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>78</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5580</v>
+        <v>6485</v>
       </c>
       <c r="C2" t="n">
-        <v>6630</v>
+        <v>8553</v>
       </c>
       <c r="D2" t="n">
-        <v>25563</v>
+        <v>25110</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4264</v>
+        <v>4525</v>
       </c>
       <c r="C3" t="n">
-        <v>3485</v>
+        <v>4246</v>
       </c>
       <c r="D3" t="n">
-        <v>12171</v>
+        <v>14377</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2600</v>
+        <v>2430</v>
       </c>
       <c r="C4" t="n">
-        <v>3913</v>
+        <v>3427</v>
       </c>
       <c r="D4" t="n">
-        <v>3567</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1509</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="n">
-        <v>3779</v>
+        <v>2532</v>
       </c>
       <c r="D5" t="n">
-        <v>1367</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>552</v>
       </c>
       <c r="C6" t="n">
-        <v>2843</v>
+        <v>1223</v>
       </c>
       <c r="D6" t="n">
-        <v>814</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>1362</v>
+        <v>503</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>420</v>
+        <v>249</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5495</v>
+        <v>5632</v>
       </c>
       <c r="C2" t="n">
-        <v>4841</v>
+        <v>6137</v>
       </c>
       <c r="D2" t="n">
-        <v>24870</v>
+        <v>24585</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4031</v>
+        <v>4521</v>
       </c>
       <c r="C3" t="n">
-        <v>4461</v>
+        <v>5735</v>
       </c>
       <c r="D3" t="n">
-        <v>13349</v>
+        <v>15059</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2940</v>
+        <v>3004</v>
       </c>
       <c r="C4" t="n">
-        <v>3559</v>
+        <v>3827</v>
       </c>
       <c r="D4" t="n">
-        <v>4993</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1785</v>
+        <v>1609</v>
       </c>
       <c r="C5" t="n">
-        <v>3772</v>
+        <v>2977</v>
       </c>
       <c r="D5" t="n">
-        <v>1726</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>3296</v>
+        <v>1912</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>2116</v>
+        <v>878</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>877</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_7_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7197</v>
+        <v>1103</v>
       </c>
       <c r="C2" t="n">
-        <v>4633</v>
+        <v>3646</v>
       </c>
       <c r="D2" t="n">
-        <v>34156</v>
+        <v>13721</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4152</v>
+        <v>2195</v>
       </c>
       <c r="C3" t="n">
-        <v>5226</v>
+        <v>6776</v>
       </c>
       <c r="D3" t="n">
-        <v>15446</v>
+        <v>12526</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3179</v>
+        <v>1595</v>
       </c>
       <c r="C4" t="n">
-        <v>4718</v>
+        <v>7914</v>
       </c>
       <c r="D4" t="n">
-        <v>8060</v>
+        <v>5527</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
+        <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>3355</v>
+        <v>5123</v>
       </c>
       <c r="D5" t="n">
-        <v>3066</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>2404</v>
+        <v>2189</v>
       </c>
       <c r="D6" t="n">
-        <v>1258</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>501</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>1394</v>
+        <v>827</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>618</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8473</v>
+        <v>1467</v>
       </c>
       <c r="C2" t="n">
-        <v>10406</v>
+        <v>7088</v>
       </c>
       <c r="D2" t="n">
-        <v>25696</v>
+        <v>20630</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4527</v>
+        <v>1424</v>
       </c>
       <c r="C3" t="n">
-        <v>4348</v>
+        <v>4459</v>
       </c>
       <c r="D3" t="n">
-        <v>16952</v>
+        <v>11825</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3083</v>
+        <v>1634</v>
       </c>
       <c r="C4" t="n">
-        <v>4868</v>
+        <v>7202</v>
       </c>
       <c r="D4" t="n">
-        <v>8942</v>
+        <v>6635</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2218</v>
+        <v>1001</v>
       </c>
       <c r="C5" t="n">
-        <v>3894</v>
+        <v>6463</v>
       </c>
       <c r="D5" t="n">
-        <v>3787</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1358</v>
+        <v>451</v>
       </c>
       <c r="C6" t="n">
-        <v>2818</v>
+        <v>3651</v>
       </c>
       <c r="D6" t="n">
-        <v>1506</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>671</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>1835</v>
+        <v>1488</v>
       </c>
       <c r="D7" t="n">
-        <v>752</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>959</v>
+        <v>576</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
         <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9108</v>
+        <v>781</v>
       </c>
       <c r="C2" t="n">
-        <v>6523</v>
+        <v>2999</v>
       </c>
       <c r="D2" t="n">
-        <v>33164</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4996</v>
+        <v>1381</v>
       </c>
       <c r="C3" t="n">
-        <v>6124</v>
+        <v>5290</v>
       </c>
       <c r="D3" t="n">
-        <v>16959</v>
+        <v>12578</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3132</v>
+        <v>1770</v>
       </c>
       <c r="C4" t="n">
-        <v>4532</v>
+        <v>6690</v>
       </c>
       <c r="D4" t="n">
-        <v>9900</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2289</v>
+        <v>993</v>
       </c>
       <c r="C5" t="n">
-        <v>4196</v>
+        <v>7457</v>
       </c>
       <c r="D5" t="n">
-        <v>4377</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1573</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>3218</v>
+        <v>4654</v>
       </c>
       <c r="D6" t="n">
-        <v>1814</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>848</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2248</v>
+        <v>1425</v>
       </c>
       <c r="D7" t="n">
-        <v>840</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>384</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1301</v>
+        <v>513</v>
       </c>
       <c r="D8" t="n">
-        <v>500</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>635</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8318</v>
+        <v>600</v>
       </c>
       <c r="C2" t="n">
-        <v>4383</v>
+        <v>3332</v>
       </c>
       <c r="D2" t="n">
-        <v>26917</v>
+        <v>12658</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5903</v>
+        <v>940</v>
       </c>
       <c r="C3" t="n">
-        <v>8497</v>
+        <v>3604</v>
       </c>
       <c r="D3" t="n">
-        <v>18840</v>
+        <v>12038</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2115</v>
+        <v>1422</v>
       </c>
       <c r="C4" t="n">
-        <v>6595</v>
+        <v>5875</v>
       </c>
       <c r="D4" t="n">
-        <v>9541</v>
+        <v>7989</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1453</v>
+        <v>1190</v>
       </c>
       <c r="C5" t="n">
-        <v>3153</v>
+        <v>7062</v>
       </c>
       <c r="D5" t="n">
-        <v>2996</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>552</v>
       </c>
       <c r="C6" t="n">
-        <v>2203</v>
+        <v>5944</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>1274</v>
+        <v>2876</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>889</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>68</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4962</v>
+        <v>368</v>
       </c>
       <c r="C2" t="n">
-        <v>2181</v>
+        <v>2087</v>
       </c>
       <c r="D2" t="n">
-        <v>19520</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5997</v>
+        <v>712</v>
       </c>
       <c r="C3" t="n">
-        <v>5936</v>
+        <v>3131</v>
       </c>
       <c r="D3" t="n">
-        <v>18853</v>
+        <v>11428</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3093</v>
+        <v>1164</v>
       </c>
       <c r="C4" t="n">
-        <v>7624</v>
+        <v>4875</v>
       </c>
       <c r="D4" t="n">
-        <v>10862</v>
+        <v>8521</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1623</v>
+        <v>1239</v>
       </c>
       <c r="C5" t="n">
-        <v>4692</v>
+        <v>6696</v>
       </c>
       <c r="D5" t="n">
-        <v>3779</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>944</v>
+        <v>682</v>
       </c>
       <c r="C6" t="n">
-        <v>2652</v>
+        <v>6586</v>
       </c>
       <c r="D6" t="n">
-        <v>1045</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>1649</v>
+        <v>4002</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>830</v>
+        <v>1359</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>452</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4942</v>
+        <v>590</v>
       </c>
       <c r="C2" t="n">
-        <v>3242</v>
+        <v>9443</v>
       </c>
       <c r="D2" t="n">
-        <v>20266</v>
+        <v>9507</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4659</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>3660</v>
+        <v>2337</v>
       </c>
       <c r="D3" t="n">
-        <v>17651</v>
+        <v>10417</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3778</v>
+        <v>863</v>
       </c>
       <c r="C4" t="n">
-        <v>6622</v>
+        <v>3936</v>
       </c>
       <c r="D4" t="n">
-        <v>11912</v>
+        <v>8736</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1998</v>
+        <v>1121</v>
       </c>
       <c r="C5" t="n">
-        <v>6001</v>
+        <v>5781</v>
       </c>
       <c r="D5" t="n">
-        <v>4820</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1139</v>
+        <v>829</v>
       </c>
       <c r="C6" t="n">
-        <v>3591</v>
+        <v>6571</v>
       </c>
       <c r="D6" t="n">
-        <v>1450</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>2106</v>
+        <v>5128</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>754</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1174</v>
+        <v>2407</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>785</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>67</v>
+      </c>
+      <c r="D14" t="n">
         <v>55</v>
-      </c>
-      <c r="D14" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2923</v>
+        <v>396</v>
       </c>
       <c r="C2" t="n">
-        <v>1508</v>
+        <v>4985</v>
       </c>
       <c r="D2" t="n">
-        <v>13979</v>
+        <v>6846</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4560</v>
+        <v>727</v>
       </c>
       <c r="C3" t="n">
-        <v>3389</v>
+        <v>4453</v>
       </c>
       <c r="D3" t="n">
-        <v>17520</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4165</v>
+        <v>1455</v>
       </c>
       <c r="C4" t="n">
-        <v>6159</v>
+        <v>5635</v>
       </c>
       <c r="D4" t="n">
-        <v>12672</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2074</v>
+        <v>838</v>
       </c>
       <c r="C5" t="n">
-        <v>6960</v>
+        <v>8881</v>
       </c>
       <c r="D5" t="n">
-        <v>5226</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>940</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>4421</v>
+        <v>6635</v>
       </c>
       <c r="D6" t="n">
-        <v>1421</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2194</v>
+        <v>2358</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>906</v>
+        <v>769</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>65</v>
+      </c>
+      <c r="D13" t="n">
         <v>53</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4397</v>
+        <v>238</v>
       </c>
       <c r="C2" t="n">
-        <v>2568</v>
+        <v>3183</v>
       </c>
       <c r="D2" t="n">
-        <v>11430</v>
+        <v>5388</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3313</v>
+        <v>496</v>
       </c>
       <c r="C3" t="n">
-        <v>2221</v>
+        <v>4151</v>
       </c>
       <c r="D3" t="n">
-        <v>15861</v>
+        <v>9754</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3789</v>
+        <v>942</v>
       </c>
       <c r="C4" t="n">
-        <v>4733</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="n">
-        <v>13077</v>
+        <v>8693</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2596</v>
+        <v>785</v>
       </c>
       <c r="C5" t="n">
-        <v>6512</v>
+        <v>6462</v>
       </c>
       <c r="D5" t="n">
-        <v>6210</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1257</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>5519</v>
+        <v>6316</v>
       </c>
       <c r="D6" t="n">
-        <v>1964</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>357</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>3152</v>
+        <v>3025</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1403</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>485</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3062</v>
+        <v>200</v>
       </c>
       <c r="C2" t="n">
-        <v>2149</v>
+        <v>5420</v>
       </c>
       <c r="D2" t="n">
-        <v>8351</v>
+        <v>10644</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>313</v>
       </c>
       <c r="C3" t="n">
-        <v>2139</v>
+        <v>3176</v>
       </c>
       <c r="D3" t="n">
-        <v>14466</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3356</v>
+        <v>644</v>
       </c>
       <c r="C4" t="n">
-        <v>3709</v>
+        <v>4327</v>
       </c>
       <c r="D4" t="n">
-        <v>13179</v>
+        <v>8632</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2837</v>
+        <v>781</v>
       </c>
       <c r="C5" t="n">
-        <v>5960</v>
+        <v>5419</v>
       </c>
       <c r="D5" t="n">
-        <v>6931</v>
+        <v>5028</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1497</v>
+        <v>468</v>
       </c>
       <c r="C6" t="n">
-        <v>6065</v>
+        <v>6382</v>
       </c>
       <c r="D6" t="n">
-        <v>2345</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>3970</v>
+        <v>4698</v>
       </c>
       <c r="D7" t="n">
-        <v>798</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1831</v>
+        <v>1908</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>557</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4743</v>
+        <v>511</v>
       </c>
       <c r="C2" t="n">
-        <v>4073</v>
+        <v>10529</v>
       </c>
       <c r="D2" t="n">
-        <v>18865</v>
+        <v>8852</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2659</v>
+        <v>221</v>
       </c>
       <c r="C3" t="n">
-        <v>1899</v>
+        <v>3774</v>
       </c>
       <c r="D3" t="n">
-        <v>12734</v>
+        <v>8108</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2873</v>
+        <v>430</v>
       </c>
       <c r="C4" t="n">
-        <v>2938</v>
+        <v>3609</v>
       </c>
       <c r="D4" t="n">
-        <v>12976</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2757</v>
+        <v>661</v>
       </c>
       <c r="C5" t="n">
-        <v>4885</v>
+        <v>4761</v>
       </c>
       <c r="D5" t="n">
-        <v>7620</v>
+        <v>5415</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1833</v>
+        <v>559</v>
       </c>
       <c r="C6" t="n">
-        <v>5969</v>
+        <v>5853</v>
       </c>
       <c r="D6" t="n">
-        <v>2930</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>649</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>4828</v>
+        <v>5488</v>
       </c>
       <c r="D7" t="n">
-        <v>986</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>2605</v>
+        <v>3164</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1019</v>
+        <v>1139</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
-        <v>193</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5831</v>
+        <v>4371</v>
       </c>
       <c r="C2" t="n">
-        <v>3580</v>
+        <v>14169</v>
       </c>
       <c r="D2" t="n">
-        <v>12808</v>
+        <v>12614</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3359</v>
+        <v>820</v>
       </c>
       <c r="C2" t="n">
-        <v>2248</v>
+        <v>20201</v>
       </c>
       <c r="D2" t="n">
-        <v>13884</v>
+        <v>15681</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>276</v>
       </c>
       <c r="C3" t="n">
-        <v>2596</v>
+        <v>5975</v>
       </c>
       <c r="D3" t="n">
-        <v>14179</v>
+        <v>7742</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4012</v>
+        <v>298</v>
       </c>
       <c r="C4" t="n">
-        <v>4511</v>
+        <v>3611</v>
       </c>
       <c r="D4" t="n">
-        <v>13465</v>
+        <v>7955</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1795</v>
+        <v>527</v>
       </c>
       <c r="C5" t="n">
-        <v>7798</v>
+        <v>4142</v>
       </c>
       <c r="D5" t="n">
-        <v>6995</v>
+        <v>5696</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>599</v>
+        <v>556</v>
       </c>
       <c r="C6" t="n">
-        <v>6018</v>
+        <v>5268</v>
       </c>
       <c r="D6" t="n">
-        <v>2266</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>2552</v>
+        <v>5643</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>998</v>
+        <v>4119</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>1921</v>
       </c>
       <c r="D9" t="n">
-        <v>189</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>645</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>38</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6245</v>
+        <v>5277</v>
       </c>
       <c r="C2" t="n">
-        <v>5168</v>
+        <v>7311</v>
       </c>
       <c r="D2" t="n">
-        <v>18227</v>
+        <v>12320</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2477</v>
+        <v>1410</v>
       </c>
       <c r="C3" t="n">
-        <v>1804</v>
+        <v>5595</v>
       </c>
       <c r="D3" t="n">
-        <v>2791</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4682</v>
+        <v>3973</v>
       </c>
       <c r="C2" t="n">
-        <v>4642</v>
+        <v>6391</v>
       </c>
       <c r="D2" t="n">
-        <v>25528</v>
+        <v>18466</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3582</v>
+        <v>2832</v>
       </c>
       <c r="C3" t="n">
-        <v>3238</v>
+        <v>5681</v>
       </c>
       <c r="D3" t="n">
-        <v>5178</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1109</v>
+        <v>678</v>
       </c>
       <c r="C4" t="n">
-        <v>1101</v>
+        <v>3538</v>
       </c>
       <c r="D4" t="n">
-        <v>1743</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6390</v>
+        <v>2449</v>
       </c>
       <c r="C2" t="n">
-        <v>7159</v>
+        <v>6632</v>
       </c>
       <c r="D2" t="n">
-        <v>22305</v>
+        <v>23395</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>2810</v>
       </c>
       <c r="C3" t="n">
-        <v>3465</v>
+        <v>5242</v>
       </c>
       <c r="D3" t="n">
-        <v>8061</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1986</v>
+        <v>1543</v>
       </c>
       <c r="C4" t="n">
-        <v>2288</v>
+        <v>4739</v>
       </c>
       <c r="D4" t="n">
-        <v>2349</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>515</v>
+        <v>336</v>
       </c>
       <c r="C5" t="n">
-        <v>695</v>
+        <v>2121</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6058</v>
+        <v>3167</v>
       </c>
       <c r="C2" t="n">
-        <v>4312</v>
+        <v>7162</v>
       </c>
       <c r="D2" t="n">
-        <v>27897</v>
+        <v>21338</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3933</v>
+        <v>2181</v>
       </c>
       <c r="C3" t="n">
-        <v>4694</v>
+        <v>5193</v>
       </c>
       <c r="D3" t="n">
-        <v>9658</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2271</v>
+        <v>1869</v>
       </c>
       <c r="C4" t="n">
-        <v>2884</v>
+        <v>4925</v>
       </c>
       <c r="D4" t="n">
-        <v>3296</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1044</v>
+        <v>785</v>
       </c>
       <c r="C5" t="n">
-        <v>1521</v>
+        <v>3509</v>
       </c>
       <c r="D5" t="n">
-        <v>1404</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>499</v>
+        <v>1241</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7246</v>
+        <v>2738</v>
       </c>
       <c r="C2" t="n">
-        <v>5810</v>
+        <v>5261</v>
       </c>
       <c r="D2" t="n">
-        <v>34661</v>
+        <v>23404</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3629</v>
+        <v>2168</v>
       </c>
       <c r="C3" t="n">
-        <v>3679</v>
+        <v>5402</v>
       </c>
       <c r="D3" t="n">
-        <v>11054</v>
+        <v>9779</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1937</v>
+        <v>1730</v>
       </c>
       <c r="C4" t="n">
-        <v>3198</v>
+        <v>4966</v>
       </c>
       <c r="D4" t="n">
-        <v>3773</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>865</v>
+        <v>1130</v>
       </c>
       <c r="C5" t="n">
-        <v>1639</v>
+        <v>4170</v>
       </c>
       <c r="D5" t="n">
-        <v>1383</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>318</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>679</v>
+        <v>2359</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>272</v>
+        <v>758</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6485</v>
+        <v>2144</v>
       </c>
       <c r="C2" t="n">
-        <v>8553</v>
+        <v>11030</v>
       </c>
       <c r="D2" t="n">
-        <v>25110</v>
+        <v>24050</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4525</v>
+        <v>2016</v>
       </c>
       <c r="C3" t="n">
-        <v>4246</v>
+        <v>4677</v>
       </c>
       <c r="D3" t="n">
-        <v>14377</v>
+        <v>11068</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2430</v>
+        <v>1649</v>
       </c>
       <c r="C4" t="n">
-        <v>3427</v>
+        <v>5080</v>
       </c>
       <c r="D4" t="n">
-        <v>5196</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1257</v>
+        <v>1235</v>
       </c>
       <c r="C5" t="n">
-        <v>2532</v>
+        <v>4425</v>
       </c>
       <c r="D5" t="n">
-        <v>1822</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>552</v>
+        <v>664</v>
       </c>
       <c r="C6" t="n">
-        <v>1223</v>
+        <v>3186</v>
       </c>
       <c r="D6" t="n">
-        <v>874</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>503</v>
+        <v>1495</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>249</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5632</v>
+        <v>2041</v>
       </c>
       <c r="C2" t="n">
-        <v>6137</v>
+        <v>6882</v>
       </c>
       <c r="D2" t="n">
-        <v>24585</v>
+        <v>19067</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4521</v>
+        <v>2796</v>
       </c>
       <c r="C3" t="n">
-        <v>5735</v>
+        <v>8186</v>
       </c>
       <c r="D3" t="n">
-        <v>15059</v>
+        <v>12084</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3004</v>
+        <v>1141</v>
       </c>
       <c r="C4" t="n">
-        <v>3827</v>
+        <v>7369</v>
       </c>
       <c r="D4" t="n">
-        <v>6750</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1609</v>
+        <v>613</v>
       </c>
       <c r="C5" t="n">
-        <v>2977</v>
+        <v>3122</v>
       </c>
       <c r="D5" t="n">
-        <v>2414</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>210</v>
       </c>
       <c r="C6" t="n">
-        <v>1912</v>
+        <v>1465</v>
       </c>
       <c r="D6" t="n">
-        <v>1034</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>878</v>
+        <v>488</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
